--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE8BD3D-8F42-495D-ACEF-46ED81E6B5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32AE465-F71B-4B65-8834-FEE93C71C6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -1271,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:N36"/>
+  <dimension ref="B1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1282,7 +1282,7 @@
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>0.44742729306487694</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1346,14 +1346,14 @@
       </c>
       <c r="J3" s="11">
         <f>+D7+F7</f>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0.33557046979865773</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+        <v>0.2796420581655481</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>0.10626398210290827</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>6.1521252796420581E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1421,14 +1421,14 @@
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>4.9217002237136459E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+        <v>0.10514541387024608</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
@@ -1436,10 +1436,10 @@
         <v>39</v>
       </c>
       <c r="D7" s="8">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F7" s="8">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="I7" s="60" t="s">
         <v>58</v>
@@ -1449,7 +1449,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1481,11 +1481,8 @@
       <c r="F10">
         <v>25</v>
       </c>
-      <c r="N10">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1502,7 +1499,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>62</v>
       </c>
@@ -1510,32 +1507,19 @@
         <v>54</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="L13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="L14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
         <f>SUM(D2:D15)</f>
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="F16" s="7">
         <f>SUM(F2:F15)</f>
-        <v>444</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1558,11 +1542,11 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5">
         <f>D17-D16</f>
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F18" s="5">
         <f>F17-F16</f>
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1667,7 +1651,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="43"/>
       <c r="I3" s="52">
-        <v>46269</v>
+        <v>46299</v>
       </c>
       <c r="J3" s="43"/>
       <c r="K3" s="53"/>
@@ -1690,7 +1674,7 @@
       <c r="G4" s="34"/>
       <c r="H4" s="34"/>
       <c r="I4" s="35">
-        <v>45872</v>
+        <v>46298</v>
       </c>
       <c r="J4" s="36"/>
       <c r="K4" s="37"/>
@@ -1710,10 +1694,10 @@
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="20">
-        <v>46268</v>
+        <v>46298</v>
       </c>
       <c r="J5" s="12">
-        <v>116.66</v>
+        <v>178.82</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1733,7 +1717,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="20">
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="J6" s="12">
         <v>38.9</v>
@@ -1780,7 +1764,7 @@
       <c r="G8" s="34"/>
       <c r="H8" s="34"/>
       <c r="I8" s="35">
-        <v>45877</v>
+        <v>46303</v>
       </c>
       <c r="J8" s="36"/>
       <c r="K8" s="37"/>
@@ -1849,7 +1833,7 @@
       <c r="G11" s="34"/>
       <c r="H11" s="34"/>
       <c r="I11" s="35">
-        <v>45885</v>
+        <v>46311</v>
       </c>
       <c r="J11" s="36"/>
       <c r="K11" s="37"/>
@@ -1890,7 +1874,7 @@
       </c>
       <c r="G13" s="12"/>
       <c r="I13" s="20">
-        <v>46272</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1918,7 +1902,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>155.56</v>
+        <v>217.72</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1957,22 +1941,24 @@
         <v>31</v>
       </c>
       <c r="B18" s="56">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="59">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E18" s="59">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="59"/>
+      <c r="G18" s="59">
+        <v>85</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>215</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1991,7 +1977,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>155.56</v>
+        <v>217.72</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2001,7 +1987,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>215</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2011,7 +1997,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>59.44</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32AE465-F71B-4B65-8834-FEE93C71C6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDFC7A9-4530-4DDA-8793-EDC549DCC011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>Totales</t>
   </si>
@@ -227,7 +230,10 @@
     <t>Way</t>
   </si>
   <si>
-    <t>%Com</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>%Com sep</t>
   </si>
 </sst>
 </file>
@@ -724,6 +730,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -869,68 +937,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -950,7 +956,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -958,17 +964,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1272,17 +1278,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1303,7 +1309,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1312,6 +1318,9 @@
       </c>
       <c r="D2" s="8">
         <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
       </c>
       <c r="F2" s="8">
         <v>60</v>
@@ -1328,7 +1337,7 @@
         <v>0.44742729306487694</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1337,6 +1346,9 @@
       </c>
       <c r="D3" s="8">
         <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
       </c>
       <c r="F3" s="8">
         <v>50</v>
@@ -1353,7 +1365,7 @@
         <v>0.2796420581655481</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1362,6 +1374,9 @@
       </c>
       <c r="D4" s="8">
         <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
       </c>
       <c r="F4" s="8">
         <v>10</v>
@@ -1378,7 +1393,7 @@
         <v>0.10626398210290827</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1387,6 +1402,9 @@
       </c>
       <c r="D5" s="8">
         <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
       </c>
       <c r="F5" s="8">
         <v>20</v>
@@ -1403,7 +1421,7 @@
         <v>6.1521252796420581E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1412,6 +1430,9 @@
       </c>
       <c r="D6" s="8">
         <v>60</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
       </c>
       <c r="F6" s="8">
         <v>60</v>
@@ -1428,7 +1449,7 @@
         <v>0.10514541387024608</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
@@ -1437,6 +1458,9 @@
       </c>
       <c r="D7" s="8">
         <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
       </c>
       <c r="F7" s="8">
         <v>125</v>
@@ -1449,7 +1473,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1459,8 +1483,11 @@
       <c r="D8" s="57">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1471,7 +1498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1482,7 +1509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1492,6 +1519,9 @@
       <c r="D11">
         <v>15</v>
       </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
       <c r="F11">
         <v>5</v>
       </c>
@@ -1499,7 +1529,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>62</v>
       </c>
@@ -1508,7 +1538,7 @@
       </c>
       <c r="K12" s="3"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
@@ -1522,7 +1552,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
@@ -1535,7 +1565,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>12</v>
       </c>
@@ -1549,24 +1579,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1578,22 +1608,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
@@ -1628,7 +1658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>36</v>
       </c>
@@ -1649,14 +1679,16 @@
         <v>53.77</v>
       </c>
       <c r="G3" s="32"/>
-      <c r="H3" s="43"/>
+      <c r="H3" s="43">
+        <v>53.77</v>
+      </c>
       <c r="I3" s="52">
-        <v>46299</v>
+        <v>46296</v>
       </c>
       <c r="J3" s="43"/>
       <c r="K3" s="53"/>
     </row>
-    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>51</v>
       </c>
@@ -1679,7 +1711,7 @@
       <c r="J4" s="36"/>
       <c r="K4" s="37"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1692,16 +1724,18 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>178.82</v>
+      </c>
       <c r="I5" s="20">
         <v>46298</v>
       </c>
       <c r="J5" s="12">
-        <v>178.82</v>
+        <v>21.75</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
       <c r="B6" t="s">
         <v>52</v>
@@ -1715,16 +1749,18 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>38.9</v>
+      </c>
       <c r="I6" s="20">
         <v>46302</v>
       </c>
       <c r="J6" s="12">
-        <v>38.9</v>
+        <v>72.05</v>
       </c>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1746,7 +1782,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33" t="s">
         <v>35</v>
       </c>
@@ -1769,7 +1805,7 @@
       <c r="J8" s="36"/>
       <c r="K8" s="37"/>
     </row>
-    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
         <v>26</v>
       </c>
@@ -1792,7 +1828,7 @@
       <c r="J9" s="43"/>
       <c r="K9" s="53"/>
     </row>
-    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1815,7 +1851,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>26</v>
       </c>
@@ -1839,7 +1875,7 @@
       <c r="K11" s="37"/>
       <c r="M11" s="34"/>
     </row>
-    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>53</v>
       </c>
@@ -1862,7 +1898,7 @@
       <c r="J12" s="41"/>
       <c r="K12" s="42"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>53</v>
       </c>
@@ -1877,7 +1913,7 @@
         <v>46302</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1897,25 +1933,25 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>271.49</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>217.72</v>
+        <v>93.8</v>
       </c>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1924,32 +1960,33 @@
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="E17" s="23">
-        <v>46295</v>
-      </c>
-      <c r="F17" s="23"/>
+        <v>46310</v>
+      </c>
+      <c r="F17" s="23">
+        <v>46326</v>
+      </c>
       <c r="G17" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="56">
-        <v>105</v>
+        <f>165+35</f>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="59">
-        <v>65</v>
-      </c>
-      <c r="E18" s="59">
         <v>30</v>
       </c>
+      <c r="E18" s="59"/>
       <c r="F18" s="2"/>
       <c r="G18" s="59">
         <v>85</v>
@@ -1958,10 +1995,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>285</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="54"/>
@@ -1970,41 +2007,41 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
       <c r="H20" s="55" t="s">
         <v>33</v>
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>217.72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>365.29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="25" t="s">
         <v>34</v>
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>285</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>43.509999999999991</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>67.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>-50.290000000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="E24" s="20"/>
       <c r="G24" s="30"/>
@@ -2013,7 +2050,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="E25" s="20"/>
       <c r="G25" s="30"/>
@@ -2022,7 +2059,7 @@
       <c r="J25"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="E26" s="20"/>
       <c r="G26" s="30"/>
@@ -2031,463 +2068,463 @@
       <c r="J26"/>
       <c r="K26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D28" s="3"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D29" s="3"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D30" s="3"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D32" s="3"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="3"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="3"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="3"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="3"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="3"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="3"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="3"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="3"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="3"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="3"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2502,14 +2539,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>44</v>
       </c>
@@ -2520,7 +2557,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="46"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2531,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="46">
         <v>46037</v>
       </c>
@@ -2546,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="46">
         <v>46053</v>
       </c>
@@ -2561,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="46">
         <v>46068</v>
       </c>
@@ -2576,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="46">
         <v>46081</v>
       </c>
@@ -2591,7 +2628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="46">
         <v>46096</v>
       </c>
@@ -2606,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="46">
         <v>46112</v>
       </c>
@@ -2621,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
         <v>46127</v>
       </c>
@@ -2636,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="46">
         <v>46142</v>
       </c>
@@ -2651,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="46">
         <v>46157</v>
       </c>
@@ -2666,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="46">
         <v>46173</v>
       </c>
@@ -2681,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
         <v>46188</v>
       </c>
@@ -2696,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="46">
         <v>46203</v>
       </c>
@@ -2711,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="46">
         <v>46218</v>
       </c>
@@ -2726,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="46">
         <v>46234</v>
       </c>
@@ -2741,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="46">
         <v>46249</v>
       </c>
@@ -2756,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="46">
         <v>46265</v>
       </c>
@@ -2771,20 +2808,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="46">
         <v>46280</v>
       </c>
       <c r="B19" s="11">
         <v>75</v>
       </c>
-      <c r="C19" s="11"/>
+      <c r="C19" s="11">
+        <v>100</v>
+      </c>
       <c r="D19" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
         <v>46295</v>
       </c>
@@ -2797,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="46">
         <v>46310</v>
       </c>
@@ -2810,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="46">
         <v>46326</v>
       </c>
@@ -2823,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="46">
         <v>46341</v>
       </c>
@@ -2836,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="46">
         <v>46356</v>
       </c>
@@ -2849,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="46">
         <v>46371</v>
       </c>
@@ -2862,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="45" t="s">
         <v>45</v>
       </c>
@@ -2875,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="45" t="s">
         <v>46</v>
       </c>
@@ -2888,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="46">
         <v>46387</v>
       </c>
@@ -2901,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="46">
         <v>46402</v>
       </c>
@@ -2914,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="46">
         <v>46418</v>
       </c>
@@ -2927,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="46">
         <v>46433</v>
       </c>
@@ -2940,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="46">
         <v>46446</v>
       </c>
@@ -2953,7 +2992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="46">
         <v>46461</v>
       </c>
@@ -2966,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="46">
         <v>46477</v>
       </c>
@@ -2979,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="46">
         <v>46492</v>
       </c>
@@ -2992,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="46">
         <v>46507</v>
       </c>
@@ -3005,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="46">
         <v>46522</v>
       </c>
@@ -3018,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="46">
         <v>46538</v>
       </c>
@@ -3031,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="46">
         <v>46553</v>
       </c>
@@ -3044,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="46">
         <v>46568</v>
       </c>
@@ -3057,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="46">
         <v>46583</v>
       </c>
@@ -3070,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="46">
         <v>46599</v>
       </c>
@@ -3083,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="46">
         <v>46614</v>
       </c>
@@ -3096,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="46">
         <v>46630</v>
       </c>
@@ -3109,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="46">
         <v>46645</v>
       </c>
@@ -3122,7 +3161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="46">
         <v>46660</v>
       </c>
@@ -3135,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="46">
         <v>46675</v>
       </c>
@@ -3148,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="46">
         <v>46691</v>
       </c>
@@ -3161,7 +3200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="46">
         <v>46706</v>
       </c>
@@ -3174,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="46">
         <v>46721</v>
       </c>
@@ -3187,7 +3226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="46">
         <v>46736</v>
       </c>
@@ -3200,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="45" t="s">
         <v>45</v>
       </c>
@@ -3213,7 +3252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="45" t="s">
         <v>46</v>
       </c>
@@ -3226,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="46">
         <v>46752</v>
       </c>
@@ -3239,44 +3278,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="49">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
       </c>
       <c r="C55" s="50">
         <f>SUM(C2:C54)</f>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="62">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-460</v>
+        <v>-435</v>
       </c>
       <c r="C57" s="63"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" s="58"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDFC7A9-4530-4DDA-8793-EDC549DCC011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF7AC64-C97E-4307-8604-928A970EB0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>Totales</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Way</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>%Com sep</t>
@@ -1319,9 +1316,6 @@
       <c r="D2" s="8">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
       <c r="F2" s="8">
         <v>60</v>
       </c>
@@ -1347,9 +1341,6 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
-        <v>63</v>
-      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
@@ -1375,9 +1366,6 @@
       <c r="D4" s="8">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
       <c r="F4" s="8">
         <v>10</v>
       </c>
@@ -1403,9 +1391,6 @@
       <c r="D5" s="8">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
       <c r="F5" s="8">
         <v>20</v>
       </c>
@@ -1431,9 +1416,6 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
@@ -1459,9 +1441,6 @@
       <c r="D7" s="8">
         <v>125</v>
       </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
       <c r="F7" s="8">
         <v>125</v>
       </c>
@@ -1483,9 +1462,6 @@
       <c r="D8" s="57">
         <v>95</v>
       </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -1518,9 +1494,6 @@
       </c>
       <c r="D11">
         <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1679,9 +1652,7 @@
         <v>53.77</v>
       </c>
       <c r="G3" s="32"/>
-      <c r="H3" s="43">
-        <v>53.77</v>
-      </c>
+      <c r="H3" s="43"/>
       <c r="I3" s="52">
         <v>46296</v>
       </c>
@@ -1731,7 +1702,7 @@
         <v>46298</v>
       </c>
       <c r="J5" s="12">
-        <v>21.75</v>
+        <v>123</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1933,12 +1904,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>271.49</v>
+        <v>217.72</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>93.8</v>
+        <v>195.05</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1969,7 +1940,7 @@
         <v>46326</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
@@ -1979,8 +1950,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="56">
-        <f>165+35</f>
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="59">
@@ -1991,11 +1961,13 @@
       <c r="G18" s="59">
         <v>85</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2">
+        <v>125</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>315</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2014,7 +1986,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>365.29</v>
+        <v>412.77</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2024,7 +1996,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>43.509999999999991</v>
+        <v>207.28</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2034,7 +2006,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>-50.290000000000006</v>
+        <v>12.22999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF7AC64-C97E-4307-8604-928A970EB0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A819DC-CF9E-43DB-AE91-CFC71C7F7208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>Totales</t>
   </si>
@@ -83,9 +80,6 @@
     <t>actual</t>
   </si>
   <si>
-    <t>Ahorro Obligatorio</t>
-  </si>
-  <si>
     <t>Colegio</t>
   </si>
   <si>
@@ -231,6 +225,18 @@
   </si>
   <si>
     <t>%Com sep</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Plan Seguro</t>
+  </si>
+  <si>
+    <t>Ahorro</t>
+  </si>
+  <si>
+    <t>CapitalPrestamo</t>
   </si>
 </sst>
 </file>
@@ -567,7 +573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -694,6 +700,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,68 +731,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -934,6 +879,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -953,7 +960,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -961,17 +968,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1274,18 +1281,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:K38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1297,21 +1304,21 @@
         <v>30</v>
       </c>
       <c r="I1" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="60" t="s">
-        <v>60</v>
-      </c>
       <c r="K1" s="60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="8">
         <v>60</v>
@@ -1320,23 +1327,23 @@
         <v>60</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" s="11">
         <f>SUM(D2:F6)</f>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="K2" s="61">
         <f>100/$J$7*J2/100</f>
-        <v>0.44742729306487694</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.72790294627383023</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="8">
         <v>50</v>
@@ -1344,24 +1351,27 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
       <c r="I3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="11">
         <f>+D7+F7</f>
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0.2796420581655481</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+        <v>5.1993067590987874E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8">
         <v>10</v>
@@ -1369,49 +1379,55 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
       <c r="I4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="11">
         <f>D8</f>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K4" s="61">
         <f t="shared" si="0"/>
-        <v>0.10626398210290827</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J5" s="11">
-        <f>SUM(D9:F11)</f>
+        <f>SUM(D11:F13)</f>
         <v>55</v>
       </c>
       <c r="K5" s="61">
         <f t="shared" si="0"/>
-        <v>6.1521252796420581E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+        <v>9.5320623916811106E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="8">
         <v>60</v>
@@ -1419,157 +1435,191 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
       <c r="I6" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J6" s="11">
-        <f>D18+F18</f>
-        <v>94</v>
+        <f>D20+F20</f>
+        <v>72</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>0.10514541387024608</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+        <v>0.1247833622183709</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="8">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J7" s="60">
         <f>SUM(J2:J6)</f>
-        <v>894</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="57">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="D8" s="57"/>
+      <c r="F8" s="57">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="D9" s="64">
+        <v>50</v>
+      </c>
+      <c r="F9" s="64"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="F10">
+      <c r="D10" s="64">
+        <v>100</v>
+      </c>
+      <c r="F10" s="64"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11">
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
         <v>15</v>
       </c>
-      <c r="F11">
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="H11">
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13">
         <v>8286917</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14">
         <v>54</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="K14" s="3"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7">
-        <f>SUM(D2:D15)</f>
-        <v>435</v>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F2:F15)</f>
-        <v>419</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7">
+        <f>SUM(D2:D17)</f>
+        <v>444</v>
+      </c>
+      <c r="F18" s="7">
+        <f>SUM(F2:F17)</f>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6">
         <f>250+250</f>
         <v>500</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F19" s="6">
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="5" t="s">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5">
-        <f>D17-D16</f>
-        <v>65</v>
-      </c>
-      <c r="F18" s="5">
-        <f>F17-F16</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5">
+        <f>D19-D18</f>
+        <v>56</v>
+      </c>
+      <c r="F20" s="5">
+        <f>F19-F18</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1581,62 +1631,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="J2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="32">
         <v>2100</v>
@@ -1645,8 +1695,8 @@
         <v>45815</v>
       </c>
       <c r="E3" s="12">
-        <f>484-Tabla1[[#This Row],[Cuota a largo plazo]]</f>
-        <v>430.23</v>
+        <f>430.23-Tabla1[[#This Row],[Cuota a largo plazo]]</f>
+        <v>376.46000000000004</v>
       </c>
       <c r="F3" s="12">
         <v>53.77</v>
@@ -1659,12 +1709,12 @@
       <c r="J3" s="43"/>
       <c r="K3" s="53"/>
     </row>
-    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="34">
         <v>700</v>
@@ -1682,12 +1732,12 @@
       <c r="J4" s="36"/>
       <c r="K4" s="37"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3">
         <v>2000</v>
@@ -1695,21 +1745,19 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12">
-        <v>178.82</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="20">
         <v>46298</v>
       </c>
       <c r="J5" s="12">
-        <v>123</v>
+        <v>152.05000000000001</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3">
         <v>840</v>
@@ -1720,9 +1768,7 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12">
-        <v>38.9</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="20">
         <v>46302</v>
       </c>
@@ -1731,12 +1777,12 @@
       </c>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3">
         <v>1925</v>
@@ -1753,12 +1799,12 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="34">
         <v>1600</v>
@@ -1776,12 +1822,12 @@
       <c r="J8" s="36"/>
       <c r="K8" s="37"/>
     </row>
-    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="32">
         <v>1500</v>
@@ -1799,12 +1845,12 @@
       <c r="J9" s="43"/>
       <c r="K9" s="53"/>
     </row>
-    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
         <v>2000</v>
@@ -1822,12 +1868,12 @@
       <c r="J10" s="12"/>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="34">
         <v>1500</v>
@@ -1846,12 +1892,12 @@
       <c r="K11" s="37"/>
       <c r="M11" s="34"/>
     </row>
-    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="39">
         <v>770</v>
@@ -1869,12 +1915,12 @@
       <c r="J12" s="41"/>
       <c r="K12" s="42"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="40">
         <v>45798</v>
@@ -1884,7 +1930,7 @@
         <v>46302</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1895,7 +1941,7 @@
       <c r="D14" s="20"/>
       <c r="E14" s="21">
         <f>+E3+F3</f>
-        <v>484</v>
+        <v>430.23</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
@@ -1904,73 +1950,65 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>217.72</v>
+        <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>195.05</v>
+        <v>224.10000000000002</v>
       </c>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23">
-        <v>46295</v>
+        <v>46310</v>
       </c>
       <c r="E17" s="23">
-        <v>46310</v>
-      </c>
-      <c r="F17" s="23">
         <v>46326</v>
       </c>
-      <c r="G17" s="23" t="s">
-        <v>63</v>
-      </c>
+      <c r="F17" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="23"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="56">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="59">
-        <v>30</v>
-      </c>
+      <c r="D18" s="59"/>
       <c r="E18" s="59"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="59">
-        <v>85</v>
-      </c>
-      <c r="H18" s="2">
-        <v>125</v>
-      </c>
+      <c r="G18" s="59"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="54"/>
@@ -1979,41 +2017,41 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>412.77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>224.10000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>207.28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>12.22999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>75.899999999999977</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="E24" s="20"/>
       <c r="G24" s="30"/>
@@ -2022,7 +2060,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="E25" s="20"/>
       <c r="G25" s="30"/>
@@ -2031,7 +2069,7 @@
       <c r="J25"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="E26" s="20"/>
       <c r="G26" s="30"/>
@@ -2040,463 +2078,463 @@
       <c r="J26"/>
       <c r="K26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D28" s="3"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D30" s="3"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D31" s="3"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D32" s="3"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="3"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="3"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="3"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="3"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="3"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="3"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="3"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="3"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="3"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="3"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2511,25 +2549,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="46"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2540,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="46">
         <v>46037</v>
       </c>
@@ -2555,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="46">
         <v>46053</v>
       </c>
@@ -2570,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="46">
         <v>46068</v>
       </c>
@@ -2585,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="46">
         <v>46081</v>
       </c>
@@ -2600,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="46">
         <v>46096</v>
       </c>
@@ -2615,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="46">
         <v>46112</v>
       </c>
@@ -2630,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="46">
         <v>46127</v>
       </c>
@@ -2645,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="46">
         <v>46142</v>
       </c>
@@ -2660,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="46">
         <v>46157</v>
       </c>
@@ -2675,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="46">
         <v>46173</v>
       </c>
@@ -2690,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="46">
         <v>46188</v>
       </c>
@@ -2705,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="46">
         <v>46203</v>
       </c>
@@ -2720,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="46">
         <v>46218</v>
       </c>
@@ -2735,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="46">
         <v>46234</v>
       </c>
@@ -2750,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="46">
         <v>46249</v>
       </c>
@@ -2765,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="46">
         <v>46265</v>
       </c>
@@ -2780,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="46">
         <v>46280</v>
       </c>
@@ -2795,7 +2833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="46">
         <v>46295</v>
       </c>
@@ -2808,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>46310</v>
       </c>
@@ -2821,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>46326</v>
       </c>
@@ -2834,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>46341</v>
       </c>
@@ -2847,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="46">
         <v>46356</v>
       </c>
@@ -2860,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="46">
         <v>46371</v>
       </c>
@@ -2873,9 +2911,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="11">
         <v>250</v>
@@ -2886,9 +2924,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="11">
         <v>315</v>
@@ -2899,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>46387</v>
       </c>
@@ -2912,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="46">
         <v>46402</v>
       </c>
@@ -2925,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="46">
         <v>46418</v>
       </c>
@@ -2938,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="46">
         <v>46433</v>
       </c>
@@ -2951,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="46">
         <v>46446</v>
       </c>
@@ -2964,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="46">
         <v>46461</v>
       </c>
@@ -2977,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="46">
         <v>46477</v>
       </c>
@@ -2990,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="46">
         <v>46492</v>
       </c>
@@ -3003,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="46">
         <v>46507</v>
       </c>
@@ -3016,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="46">
         <v>46522</v>
       </c>
@@ -3029,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="46">
         <v>46538</v>
       </c>
@@ -3042,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="46">
         <v>46553</v>
       </c>
@@ -3055,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="46">
         <v>46568</v>
       </c>
@@ -3068,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="46">
         <v>46583</v>
       </c>
@@ -3081,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="46">
         <v>46599</v>
       </c>
@@ -3094,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="46">
         <v>46614</v>
       </c>
@@ -3107,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="46">
         <v>46630</v>
       </c>
@@ -3120,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="46">
         <v>46645</v>
       </c>
@@ -3133,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="46">
         <v>46660</v>
       </c>
@@ -3146,7 +3184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="46">
         <v>46675</v>
       </c>
@@ -3159,7 +3197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="46">
         <v>46691</v>
       </c>
@@ -3172,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="46">
         <v>46706</v>
       </c>
@@ -3185,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="46">
         <v>46721</v>
       </c>
@@ -3198,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="46">
         <v>46736</v>
       </c>
@@ -3211,9 +3249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="11">
         <v>250</v>
@@ -3224,9 +3262,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" s="11">
         <v>315</v>
@@ -3237,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="46">
         <v>46752</v>
       </c>
@@ -3250,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="49">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3260,34 +3298,34 @@
         <v>800</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="62">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-435</v>
+        <v>-505</v>
       </c>
       <c r="C57" s="63"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="58"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A819DC-CF9E-43DB-AE91-CFC71C7F7208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B938F53F-0246-45CB-8249-D2664362F280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>Totales</t>
   </si>
@@ -227,16 +227,13 @@
     <t>%Com sep</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>Plan Seguro</t>
-  </si>
-  <si>
     <t>Ahorro</t>
   </si>
   <si>
     <t>CapitalPrestamo</t>
+  </si>
+  <si>
+    <t>Deuda corta</t>
   </si>
 </sst>
 </file>
@@ -573,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -694,13 +691,19 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1281,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:K38"/>
+  <dimension ref="B1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1331,11 +1334,11 @@
       </c>
       <c r="J2" s="11">
         <f>SUM(D2:F6)</f>
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="K2" s="61">
-        <f>100/$J$7*J2/100</f>
-        <v>0.72790294627383023</v>
+        <f>100/$J$8*J2/100</f>
+        <v>0.46413502109704646</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -1351,19 +1354,16 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
       <c r="I3" s="9" t="s">
         <v>54</v>
       </c>
       <c r="J3" s="11">
-        <f>+D7+F7</f>
-        <v>30</v>
+        <f>+D9</f>
+        <v>50</v>
       </c>
       <c r="K3" s="61">
-        <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>5.1993067590987874E-2</v>
+        <f t="shared" ref="K3:K7" si="0">100/$J$8*J3/100</f>
+        <v>5.2742616033755275E-2</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -1379,19 +1379,16 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
-        <v>63</v>
-      </c>
       <c r="I4" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J4" s="11">
-        <f>D8</f>
-        <v>0</v>
+        <f>+F8+D10</f>
+        <v>267</v>
       </c>
       <c r="K4" s="61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28164556962025317</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -1402,13 +1399,10 @@
         <v>16</v>
       </c>
       <c r="D5" s="8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F5" s="8">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>56</v>
@@ -1419,7 +1413,7 @@
       </c>
       <c r="K5" s="61">
         <f t="shared" si="0"/>
-        <v>9.5320623916811106E-2</v>
+        <v>5.8016877637130808E-2</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -1435,40 +1429,33 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>63</v>
-      </c>
       <c r="I6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="J6" s="11">
         <f>D20+F20</f>
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>0.1247833622183709</v>
+        <v>8.6497890295358648E-2</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="8">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8">
-        <v>15</v>
-      </c>
-      <c r="I7" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="60">
-        <f>SUM(J2:J6)</f>
-        <v>577</v>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="I7" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="66">
+        <f>+D14</f>
+        <v>54</v>
+      </c>
+      <c r="K7" s="61">
+        <f t="shared" si="0"/>
+        <v>5.6962025316455694E-2</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -1478,34 +1465,43 @@
       <c r="C8" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="57"/>
+      <c r="D8" s="57">
+        <v>0</v>
+      </c>
       <c r="F8" s="57">
         <v>167</v>
       </c>
+      <c r="I8" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="68">
+        <f>SUM(J2:J7)</f>
+        <v>948</v>
+      </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="62">
         <v>50</v>
       </c>
-      <c r="F9" s="64"/>
+      <c r="F9" s="62"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="62">
         <v>100</v>
       </c>
-      <c r="F10" s="64"/>
+      <c r="F10" s="62"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -1528,9 +1524,6 @@
       <c r="F12">
         <v>25</v>
       </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -1545,12 +1538,6 @@
       <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13">
-        <v>8286917</v>
-      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
@@ -1559,7 +1546,12 @@
       <c r="D14">
         <v>54</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="H14">
+        <v>8286917</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K15" s="3"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
@@ -1568,11 +1560,11 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7">
         <f>SUM(D2:D17)</f>
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F18" s="7">
         <f>SUM(F2:F17)</f>
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1595,11 +1587,11 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5">
         <f>D19-D18</f>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F20" s="5">
         <f>F19-F18</f>
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -1607,19 +1599,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="50" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
-      <formula>$C$7</formula>
+    <cfRule type="cellIs" dxfId="16" priority="51" operator="equal">
+      <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="52" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="53" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1745,12 +1737,14 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>187.79</v>
+      </c>
       <c r="I5" s="20">
         <v>46298</v>
       </c>
       <c r="J5" s="12">
-        <v>152.05000000000001</v>
+        <v>13.65</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1768,13 +1762,13 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>157.4</v>
+      </c>
       <c r="I6" s="20">
         <v>46302</v>
       </c>
-      <c r="J6" s="12">
-        <v>72.05</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1950,12 +1944,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>345.19</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>224.10000000000002</v>
+        <v>13.65</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1994,18 +1988,24 @@
         <v>30</v>
       </c>
       <c r="B18" s="56">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="2"/>
+      <c r="D18" s="59">
+        <v>60</v>
+      </c>
+      <c r="E18" s="59">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2">
+        <v>370</v>
+      </c>
       <c r="G18" s="59"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>224.10000000000002</v>
+        <v>358.84</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>300</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>75.899999999999977</v>
+        <v>91.16</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D19" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3303,11 +3303,11 @@
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="62">
+      <c r="B57" s="63">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-505</v>
       </c>
-      <c r="C57" s="63"/>
+      <c r="C57" s="64"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="58"/>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B938F53F-0246-45CB-8249-D2664362F280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E202CFB-FCBA-4F3C-B823-5A4E3DD8D8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
   <si>
     <t>Totales</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Deuda corta</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -570,7 +573,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -692,18 +695,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1351,6 +1350,9 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
@@ -1426,6 +1428,9 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
+      <c r="E6" t="s">
+        <v>66</v>
+      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
@@ -1442,14 +1447,12 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
       <c r="D7" s="57"/>
       <c r="F7" s="57"/>
-      <c r="I7" s="67" t="s">
+      <c r="I7" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="12">
         <f>+D14</f>
         <v>54</v>
       </c>
@@ -1474,7 +1477,7 @@
       <c r="I8" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="68">
+      <c r="J8" s="64">
         <f>SUM(J2:J7)</f>
         <v>948</v>
       </c>
@@ -1535,6 +1538,9 @@
       <c r="D13">
         <v>15</v>
       </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
       <c r="F13">
         <v>5</v>
       </c>
@@ -1553,7 +1559,12 @@
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="K15" s="3"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
@@ -1567,7 +1578,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>11</v>
       </c>
@@ -1580,7 +1591,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
@@ -1594,7 +1605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>42</v>
       </c>
@@ -3303,11 +3314,11 @@
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="63">
+      <c r="B57" s="65">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-505</v>
-      </c>
-      <c r="C57" s="64"/>
+        <v>-580</v>
+      </c>
+      <c r="C57" s="66"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="58"/>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E202CFB-FCBA-4F3C-B823-5A4E3DD8D8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4B29BF-1EA4-4D01-B6F9-7EA2517AD018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>Totales</t>
   </si>
@@ -234,9 +237,6 @@
   </si>
   <si>
     <t>Deuda corta</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -404,7 +404,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -526,19 +526,6 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="thin">
@@ -573,7 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -672,9 +659,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -682,12 +666,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -695,7 +679,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -923,7 +907,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1284,17 +1268,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1305,17 +1289,17 @@
       <c r="F1" s="13">
         <v>30</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="J1" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="60" t="s">
+      <c r="K1" s="59" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1335,12 +1319,12 @@
         <f>SUM(D2:F6)</f>
         <v>440</v>
       </c>
-      <c r="K2" s="61">
+      <c r="K2" s="60">
         <f>100/$J$8*J2/100</f>
         <v>0.46413502109704646</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1349,9 +1333,6 @@
       </c>
       <c r="D3" s="8">
         <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>66</v>
       </c>
       <c r="F3" s="8">
         <v>50</v>
@@ -1363,12 +1344,12 @@
         <f>+D9</f>
         <v>50</v>
       </c>
-      <c r="K3" s="61">
+      <c r="K3" s="60">
         <f t="shared" ref="K3:K7" si="0">100/$J$8*J3/100</f>
         <v>5.2742616033755275E-2</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1388,12 +1369,12 @@
         <f>+F8+D10</f>
         <v>267</v>
       </c>
-      <c r="K4" s="61">
+      <c r="K4" s="60">
         <f t="shared" si="0"/>
         <v>0.28164556962025317</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1413,12 +1394,12 @@
         <f>SUM(D11:F13)</f>
         <v>55</v>
       </c>
-      <c r="K5" s="61">
+      <c r="K5" s="60">
         <f t="shared" si="0"/>
         <v>5.8016877637130808E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1427,9 +1408,6 @@
       </c>
       <c r="D6" s="8">
         <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>66</v>
       </c>
       <c r="F6" s="8">
         <v>60</v>
@@ -1441,72 +1419,72 @@
         <f>D20+F20</f>
         <v>82</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="60">
         <f t="shared" si="0"/>
         <v>8.6497890295358648E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="I7" s="63" t="s">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="I7" s="62" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="12">
         <f>+D14</f>
         <v>54</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="60">
         <f t="shared" si="0"/>
         <v>5.6962025316455694E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="57">
-        <v>0</v>
-      </c>
-      <c r="F8" s="57">
+      <c r="D8" s="56">
+        <v>0</v>
+      </c>
+      <c r="F8" s="56">
         <v>167</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="I8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="63">
         <f>SUM(J2:J7)</f>
         <v>948</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>63</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="61">
         <v>50</v>
       </c>
-      <c r="F9" s="62"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F9" s="61"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="61">
         <v>100</v>
       </c>
-      <c r="F10" s="62"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F10" s="61"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -1517,7 +1495,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>9</v>
       </c>
@@ -1538,14 +1516,11 @@
       <c r="D13">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
-        <v>66</v>
-      </c>
       <c r="F13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -1556,15 +1531,10 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K15" s="3"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J17">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
@@ -1578,7 +1548,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>11</v>
       </c>
@@ -1591,7 +1561,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
@@ -1605,12 +1575,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="cellIs" dxfId="17" priority="50" operator="equal">
@@ -1634,22 +1604,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>15</v>
       </c>
@@ -1684,17 +1654,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+    <row r="3" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="50" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="32">
         <v>2100</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="51">
         <v>45815</v>
       </c>
       <c r="E3" s="12">
@@ -1706,13 +1676,13 @@
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="43"/>
-      <c r="I3" s="52">
+      <c r="I3" s="51">
         <v>46296</v>
       </c>
       <c r="J3" s="43"/>
-      <c r="K3" s="53"/>
-    </row>
-    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="52"/>
+    </row>
+    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>50</v>
       </c>
@@ -1735,7 +1705,7 @@
       <c r="J4" s="36"/>
       <c r="K4" s="37"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1759,7 +1729,7 @@
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
       <c r="B6" t="s">
         <v>51</v>
@@ -1779,10 +1749,12 @@
       <c r="I6" s="20">
         <v>46302</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="12">
+        <v>50</v>
+      </c>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1804,7 +1776,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33" t="s">
         <v>34</v>
       </c>
@@ -1827,30 +1799,30 @@
       <c r="J8" s="36"/>
       <c r="K8" s="37"/>
     </row>
-    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+    <row r="9" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="32">
         <v>1500</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="51">
         <v>45826</v>
       </c>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="52">
+      <c r="I9" s="51">
         <v>45943</v>
       </c>
       <c r="J9" s="43"/>
-      <c r="K9" s="53"/>
-    </row>
-    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="52"/>
+    </row>
+    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1873,7 +1845,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>25</v>
       </c>
@@ -1897,7 +1869,7 @@
       <c r="K11" s="37"/>
       <c r="M11" s="34"/>
     </row>
-    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>52</v>
       </c>
@@ -1920,7 +1892,7 @@
       <c r="J12" s="41"/>
       <c r="K12" s="42"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>52</v>
       </c>
@@ -1935,7 +1907,7 @@
         <v>46302</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1960,20 +1932,20 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>13.65</v>
+        <v>63.65</v>
       </c>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,75 +1966,73 @@
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="56">
-        <v>0</v>
+      <c r="B18" s="55">
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="59">
-        <v>60</v>
-      </c>
-      <c r="E18" s="59">
+      <c r="D18" s="58"/>
+      <c r="E18" s="58">
         <v>20</v>
       </c>
       <c r="F18" s="2">
         <v>370</v>
       </c>
-      <c r="G18" s="59"/>
+      <c r="G18" s="58"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
-      <c r="H20" s="55" t="s">
+      <c r="H20" s="54" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>358.84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>408.84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="25" t="s">
         <v>33</v>
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>104.81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>234.81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>91.16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>171.16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="E24" s="20"/>
       <c r="G24" s="30"/>
@@ -2071,7 +2041,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="E25" s="20"/>
       <c r="G25" s="30"/>
@@ -2080,7 +2050,7 @@
       <c r="J25"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="E26" s="20"/>
       <c r="G26" s="30"/>
@@ -2089,418 +2059,418 @@
       <c r="J26"/>
       <c r="K26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D28" s="3"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D29" s="3"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D30" s="3"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D32" s="3"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="3"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="3"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="3"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="3"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="3"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="3"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="3"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="3"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="3"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="3"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
@@ -2559,15 +2529,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>43</v>
       </c>
@@ -2578,98 +2548,92 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="46">
+        <v>46310</v>
+      </c>
       <c r="B2" s="11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" t="b">
-        <f t="shared" ref="D2:D28" ca="1" si="0">AND(TEXT(A2,"mm-yyyy")=TEXT(TODAY()-DAY(TODAY()-1),"mm-yyyy"), C2&gt;=B2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D2:D9" ca="1" si="0">AND(TEXT(A2,"mm-yyyy")=TEXT(TODAY()-DAY(TODAY()-1),"mm-yyyy"), C2&gt;=B2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="46">
-        <v>46037</v>
-      </c>
-      <c r="B3" s="11">
-        <v>75</v>
-      </c>
+        <v>46326</v>
+      </c>
+      <c r="B3" s="11"/>
       <c r="C3" s="11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D3" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="46">
-        <v>46053</v>
+        <v>46341</v>
       </c>
       <c r="B4" s="11">
-        <v>70</v>
-      </c>
-      <c r="C4" s="11">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C4" s="11"/>
       <c r="D4" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="46">
-        <v>46068</v>
-      </c>
-      <c r="B5" s="11">
-        <v>75</v>
-      </c>
+        <v>46356</v>
+      </c>
+      <c r="B5" s="11"/>
       <c r="C5" s="11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="46">
-        <v>46081</v>
+        <v>46371</v>
       </c>
       <c r="B6" s="11">
-        <v>70</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C6" s="11"/>
       <c r="D6" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="46">
-        <v>46096</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
+        <v>44</v>
       </c>
       <c r="B7" s="11">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C7" s="11">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D7" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="46">
-        <v>46112</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
+        <v>45</v>
       </c>
       <c r="B8" s="11">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C8" s="11">
         <v>100</v>
@@ -2679,13 +2643,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
-        <v>46127</v>
-      </c>
-      <c r="B9" s="11">
-        <v>75</v>
-      </c>
+        <v>46387</v>
+      </c>
+      <c r="B9" s="11"/>
       <c r="C9" s="11">
         <v>100</v>
       </c>
@@ -2694,292 +2656,272 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="46">
-        <v>46142</v>
+        <v>46402</v>
       </c>
       <c r="B10" s="11">
-        <v>70</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C10" s="11"/>
       <c r="D10" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D10:D35" ca="1" si="1">AND(TEXT(A10,"mm-yyyy")=TEXT(TODAY()-DAY(TODAY()-1),"mm-yyyy"), C10&gt;=B10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="46">
-        <v>46157</v>
-      </c>
-      <c r="B11" s="11">
-        <v>75</v>
-      </c>
+        <v>46418</v>
+      </c>
+      <c r="B11" s="11"/>
       <c r="C11" s="11">
+        <v>100</v>
+      </c>
+      <c r="D11" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="46">
+        <v>46433</v>
+      </c>
+      <c r="B12" s="11">
         <v>50</v>
       </c>
-      <c r="D11" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="46">
-        <v>46173</v>
-      </c>
-      <c r="B12" s="11">
-        <v>70</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="C12" s="11"/>
+      <c r="D12" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="46">
+        <v>46446</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11">
+        <v>100</v>
+      </c>
+      <c r="D13" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="46">
+        <v>46461</v>
+      </c>
+      <c r="B14" s="11">
         <v>50</v>
       </c>
-      <c r="D12" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="46">
-        <v>46188</v>
-      </c>
-      <c r="B13" s="11">
-        <v>75</v>
-      </c>
-      <c r="C13" s="11">
+      <c r="C14" s="11"/>
+      <c r="D14" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="46">
+        <v>46477</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11">
+        <v>100</v>
+      </c>
+      <c r="D15" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="46">
+        <v>46492</v>
+      </c>
+      <c r="B16" s="11">
         <v>50</v>
       </c>
-      <c r="D13" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="46">
-        <v>46203</v>
-      </c>
-      <c r="B14" s="11">
-        <v>70</v>
-      </c>
-      <c r="C14" s="11">
-        <v>0</v>
-      </c>
-      <c r="D14" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="46">
-        <v>46218</v>
-      </c>
-      <c r="B15" s="11">
-        <v>75</v>
-      </c>
-      <c r="C15" s="11">
-        <v>0</v>
-      </c>
-      <c r="D15" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="46">
-        <v>46234</v>
-      </c>
-      <c r="B16" s="11">
-        <v>70</v>
-      </c>
-      <c r="C16" s="11">
-        <v>0</v>
-      </c>
+      <c r="C16" s="11"/>
       <c r="D16" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="46">
-        <v>46249</v>
-      </c>
-      <c r="B17" s="11">
-        <v>75</v>
-      </c>
+        <v>46507</v>
+      </c>
+      <c r="B17" s="11"/>
       <c r="C17" s="11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="46">
-        <v>46265</v>
+        <v>46522</v>
       </c>
       <c r="B18" s="11">
-        <v>70</v>
-      </c>
-      <c r="C18" s="11">
-        <v>150</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C18" s="11"/>
       <c r="D18" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="46">
-        <v>46280</v>
-      </c>
-      <c r="B19" s="11">
-        <v>75</v>
-      </c>
+        <v>46538</v>
+      </c>
+      <c r="B19" s="11"/>
       <c r="C19" s="11">
         <v>100</v>
       </c>
       <c r="D19" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
-        <v>46295</v>
+        <v>46553</v>
       </c>
       <c r="B20" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="46">
-        <v>46310</v>
-      </c>
-      <c r="B21" s="11">
-        <v>75</v>
-      </c>
-      <c r="C21" s="11"/>
+        <v>46568</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11">
+        <v>100</v>
+      </c>
       <c r="D21" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="46">
-        <v>46326</v>
+        <v>46583</v>
       </c>
       <c r="B22" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="46">
-        <v>46341</v>
-      </c>
-      <c r="B23" s="11">
-        <v>75</v>
-      </c>
-      <c r="C23" s="11"/>
+        <v>46599</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11">
+        <v>100</v>
+      </c>
       <c r="D23" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="46">
-        <v>46356</v>
+        <v>46614</v>
       </c>
       <c r="B24" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="46">
-        <v>46371</v>
-      </c>
-      <c r="B25" s="11">
-        <v>75</v>
-      </c>
-      <c r="C25" s="11"/>
+        <v>46630</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11">
+        <v>100</v>
+      </c>
       <c r="D25" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
-        <v>44</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="46">
+        <v>46645</v>
       </c>
       <c r="B26" s="11">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="11">
-        <v>315</v>
-      </c>
-      <c r="C27" s="11"/>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="46">
+        <v>46660</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11">
+        <v>100</v>
+      </c>
       <c r="D27" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="46">
-        <v>46387</v>
+        <v>46675</v>
       </c>
       <c r="B28" s="11">
-        <v>70</v>
-      </c>
-      <c r="C28" s="48"/>
+        <v>50</v>
+      </c>
+      <c r="C28" s="11"/>
       <c r="D28" t="b">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="46">
-        <v>46402</v>
-      </c>
-      <c r="B29" s="11">
-        <v>75</v>
-      </c>
-      <c r="C29" s="11"/>
+        <v>46691</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11">
+        <v>100</v>
+      </c>
       <c r="D29" t="b">
-        <f t="shared" ref="D29:D54" ca="1" si="1">AND(TEXT(A29,"mm-yyyy")=TEXT(TODAY()-DAY(TODAY()-1),"mm-yyyy"), C29&gt;=B29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="46">
-        <v>46418</v>
+        <v>46706</v>
       </c>
       <c r="B30" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" t="b">
@@ -2987,25 +2929,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="46">
-        <v>46433</v>
-      </c>
-      <c r="B31" s="11">
-        <v>75</v>
-      </c>
-      <c r="C31" s="11"/>
+        <v>46721</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11">
+        <v>100</v>
+      </c>
       <c r="D31" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="46">
-        <v>46446</v>
+        <v>46736</v>
       </c>
       <c r="B32" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" t="b">
@@ -3013,338 +2955,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="46">
-        <v>46461</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="45" t="s">
+        <v>44</v>
       </c>
       <c r="B33" s="11">
-        <v>75</v>
-      </c>
-      <c r="C33" s="11"/>
+        <v>100</v>
+      </c>
+      <c r="C33" s="11">
+        <v>100</v>
+      </c>
       <c r="D33" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="46">
-        <v>46477</v>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="45" t="s">
+        <v>45</v>
       </c>
       <c r="B34" s="11">
-        <v>70</v>
-      </c>
-      <c r="C34" s="11"/>
+        <v>100</v>
+      </c>
+      <c r="C34" s="11">
+        <v>100</v>
+      </c>
       <c r="D34" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="46">
-        <v>46492</v>
-      </c>
-      <c r="B35" s="11">
-        <v>75</v>
-      </c>
-      <c r="C35" s="11"/>
+        <v>46752</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11">
+        <v>100</v>
+      </c>
       <c r="D35" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="46">
-        <v>46507</v>
-      </c>
-      <c r="B36" s="11">
-        <v>70</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="46">
-        <v>46522</v>
-      </c>
-      <c r="B37" s="11">
-        <v>75</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="46">
-        <v>46538</v>
-      </c>
-      <c r="B38" s="11">
-        <v>70</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="46">
-        <v>46553</v>
-      </c>
-      <c r="B39" s="11">
-        <v>75</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="46">
-        <v>46568</v>
-      </c>
-      <c r="B40" s="11">
-        <v>70</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="46">
-        <v>46583</v>
-      </c>
-      <c r="B41" s="11">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="46">
-        <v>46599</v>
-      </c>
-      <c r="B42" s="11">
-        <v>70</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="D42" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="46">
-        <v>46614</v>
-      </c>
-      <c r="B43" s="11">
-        <v>75</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="46">
-        <v>46630</v>
-      </c>
-      <c r="B44" s="11">
-        <v>70</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="D44" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="46">
-        <v>46645</v>
-      </c>
-      <c r="B45" s="11">
-        <v>75</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="46">
-        <v>46660</v>
-      </c>
-      <c r="B46" s="11">
-        <v>70</v>
-      </c>
-      <c r="C46" s="11"/>
-      <c r="D46" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="46">
-        <v>46675</v>
-      </c>
-      <c r="B47" s="11">
-        <v>75</v>
-      </c>
-      <c r="C47" s="11"/>
-      <c r="D47" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="46">
-        <v>46691</v>
-      </c>
-      <c r="B48" s="11">
-        <v>70</v>
-      </c>
-      <c r="C48" s="11"/>
-      <c r="D48" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="46">
-        <v>46706</v>
-      </c>
-      <c r="B49" s="11">
-        <v>75</v>
-      </c>
-      <c r="C49" s="11"/>
-      <c r="D49" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="46">
-        <v>46721</v>
-      </c>
-      <c r="B50" s="11">
-        <v>70</v>
-      </c>
-      <c r="C50" s="11"/>
-      <c r="D50" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="46">
-        <v>46736</v>
-      </c>
-      <c r="B51" s="11">
-        <v>75</v>
-      </c>
-      <c r="C51" s="11"/>
-      <c r="D51" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="11">
-        <v>250</v>
-      </c>
-      <c r="C52" s="11"/>
-      <c r="D52" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="11">
-        <v>315</v>
-      </c>
-      <c r="C53" s="11"/>
-      <c r="D53" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="46">
-        <v>46752</v>
-      </c>
-      <c r="B54" s="11">
-        <v>70</v>
-      </c>
-      <c r="C54" s="48"/>
-      <c r="D54" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="49">
-        <f>SUM(B2:B54)</f>
-        <v>4610</v>
-      </c>
-      <c r="C55" s="50">
-        <f>SUM(C2:C54)</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-    </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="65">
-        <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-580</v>
-      </c>
-      <c r="C57" s="66"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="58"/>
-      <c r="C58" s="3"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B59"/>
-      <c r="C59" s="3"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+    <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="48">
+        <f>SUM(B2:B35)</f>
+        <v>1150</v>
+      </c>
+      <c r="C36" s="49">
+        <f>SUM(C2:C35)</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="64">
+        <f ca="1">IFERROR(SUMIFS(C2:C35,A2:A35,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B35,A2:A35,"&lt;="&amp;TODAY()),0)</f>
+        <v>-50</v>
+      </c>
+      <c r="C38" s="65"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="57"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
-  <conditionalFormatting sqref="B57:C57">
+  <conditionalFormatting sqref="B38:C38">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
